--- a/project/outputs_xlsx_solution/prog-noloop.1-wide.xlsx
+++ b/project/outputs_xlsx_solution/prog-noloop.1-wide.xlsx
@@ -59,13 +59,16 @@
     <t>addi X2, X0, 124</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
   </si>
   <si>
     <t>fld F2, 200(X0)</t>
   </si>
   <si>
-    <t>WB/CT</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>fld F0, 0(X1)</t>
@@ -80,12 +83,12 @@
     <t>fadd F0, F0, F4</t>
   </si>
   <si>
-    <t>EX</t>
-  </si>
-  <si>
     <t>fsd F0, 0(X2)</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>addi X1, X1, -8</t>
   </si>
   <si>
@@ -101,13 +104,40 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -519,6 +549,12 @@
       <c r="R1">
         <v>15</v>
       </c>
+      <c r="S1">
+        <v>16</v>
+      </c>
+      <c r="T1">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -540,7 +576,7 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -563,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -586,7 +622,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +633,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>5</v>
@@ -609,7 +645,7 @@
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
@@ -632,16 +668,16 @@
         <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +688,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>5</v>
@@ -666,8 +702,8 @@
       <c r="L7" t="s">
         <v>10</v>
       </c>
-      <c r="N7" t="s">
-        <v>10</v>
+      <c r="O7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +714,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
         <v>5</v>
@@ -687,19 +723,19 @@
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -719,13 +755,13 @@
         <v>6</v>
       </c>
       <c r="M9" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="R9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -736,7 +772,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L10" t="s">
         <v>5</v>
@@ -750,8 +786,8 @@
       <c r="O10" t="s">
         <v>10</v>
       </c>
-      <c r="R10" t="s">
-        <v>10</v>
+      <c r="S10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -762,7 +798,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
         <v>5</v>
@@ -776,13 +812,13 @@
       <c r="P11" t="s">
         <v>10</v>
       </c>
-      <c r="R11" t="s">
-        <v>10</v>
+      <c r="T11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -790,7 +826,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -798,23 +834,23 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -822,7 +858,47 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
